--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:42</t>
+    <t xml:space="preserve">2026-09-09 22:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:29</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
@@ -36,16 +36,22 @@
     <t xml:space="preserve">Aysén</t>
   </si>
   <si>
+    <t xml:space="preserve">Cochrane</t>
+  </si>
+  <si>
     <t xml:space="preserve">Río Ibáñez</t>
   </si>
   <si>
-    <t xml:space="preserve">Cochrane</t>
+    <t xml:space="preserve">Cisnes</t>
   </si>
   <si>
     <t xml:space="preserve">Chile Chico</t>
   </si>
   <si>
-    <t xml:space="preserve">Cisnes</t>
+    <t xml:space="preserve">Coyhaique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tortel</t>
   </si>
   <si>
     <t xml:space="preserve">O'Higgins</t>
@@ -54,22 +60,16 @@
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">Tortel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Guaitecas</t>
   </si>
   <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,16 +493,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>11402</v>
+        <v>11201</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>585</v>
+        <v>919</v>
       </c>
     </row>
     <row r="3">
@@ -510,16 +510,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>11201</v>
+        <v>11301</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>265</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4">
@@ -530,13 +530,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11301</v>
+        <v>11402</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5">
@@ -547,13 +547,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11401</v>
+        <v>11202</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>86</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6">
@@ -564,13 +564,13 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>11202</v>
+        <v>11401</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>64</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11302</v>
+        <v>11101</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
@@ -598,13 +598,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>11102</v>
+        <v>11303</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -615,13 +615,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>11303</v>
+        <v>11302</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -632,13 +632,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11203</v>
+        <v>11102</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-157</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="11">
@@ -649,13 +649,13 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>11101</v>
+        <v>11203</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-645</v>
+        <v>-63</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:24</t>
+    <t xml:space="preserve">2026-09-27 22:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:12</t>
+    <t xml:space="preserve">2026-10-01 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:53</t>
+    <t xml:space="preserve">2026-10-02 13:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:20</t>
+    <t xml:space="preserve">2026-10-04 08:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:07</t>
+    <t xml:space="preserve">2026-10-05 07:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
